--- a/sampleprojects/TaxReturn/excel/states/MT.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/MT.xlsx
@@ -83,7 +83,7 @@
     <t>MFJ/QSS: $29,200 std ded, 5.9%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 29200.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.059</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 29200.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.059</t>
   </si>
   <si>
     <t>X</t>
@@ -92,13 +92,13 @@
     <t>HOH: $21,900 std ded, 5.9%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 21900.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.059</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 21900.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.059</t>
   </si>
   <si>
     <t>Default (Single/MFS): $14,600 std ded, 5.9%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 14600.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.059</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 14600.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.059</t>
   </si>
   <si>
     <t>Policy:</t>

--- a/sampleprojects/TaxReturn/excel/states/MT.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/MT.xlsx
@@ -257,7 +257,7 @@
     <t>0.0</t>
   </si>
   <si>
-    <t>MT taxable military retirement after exemption (computed)</t>
+    <t>MT taxable military retirement: all of it unless Form WMRE applies (see mt_new_resident_deduction_rate). Montana has no other military retirement subtraction for 2025 (Form 2 instructions; MCA 15-30-2120).</t>
   </si>
   <si>
     <t>mt_national_guard_exemption</t>
@@ -275,7 +275,7 @@
     <t>0.50</t>
   </si>
   <si>
-    <t>MT new resident deduction: 50% of military retirement (2025). Source: MOAA State Report Card</t>
+    <t>Montana working military retiree subtraction (Form 2 Schedule I line 13, Form WMRE; MCA 15-30-2120(3)(n)): the lesser of Montana source wage income and 50% of the military retirement income, for five consecutive years, only for a retiree who became a resident on or after June 30, 2023 or was a resident before the pay began. Needs residency and retirement dates the data model does not carry, so the rules subtract nothing (#1330).</t>
   </si>
   <si>
     <t>mt_new_resident_year_limit</t>
